--- a/data/describe/few_shot/few_shot_cluster_description.xlsx
+++ b/data/describe/few_shot/few_shot_cluster_description.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\describe\few_shot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB02DE13-1D10-4DA6-8F85-0F141FB34304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA453674-EBD1-4C0D-97DC-64FE61C99234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="390" windowWidth="17010" windowHeight="10110" xr2:uid="{75A2F0CC-120C-46DD-B882-D3F79246B1DD}"/>
+    <workbookView xWindow="29940" yWindow="1140" windowWidth="38700" windowHeight="15225" xr2:uid="{75A2F0CC-120C-46DD-B882-D3F79246B1DD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -45,28 +45,28 @@
     <t>Assistant</t>
   </si>
   <si>
-    <t>Entities in this cluster are grounded and empathetic, while being slightly less reserved. They show normal levels of modesty, conscientiousness, and consideration, as well as typical casualness, giving them a stable and thoughtful style.
-Their strengths include being very grounded and relatively empathetic, which helps them stay practical, reliable, and understanding of others.
-Their weaknesses are being slightly reserved.</t>
-  </si>
-  <si>
-    <t>Entities in this cluster are outgoing and carefree, while being slightly less reserved and imaginative, giving them a relaxed and sociable style.
-They are outgoing and carefree, making them comfortable and confident in social settings.
-Their weaknesses are minor being less reserved and imaginative may sometimes lead to less caution, planning, or reflection.</t>
-  </si>
-  <si>
-    <t>Entities in this cluster are generally well-balanced. They show normal levels of outgoing, thoughtful, and casual traits, while being somewhat more outgoing, candid, and conventional, with a bit higher empathy.
-Their strengths include being very outgoing and empathetic, which enables them to communicate clearly, be reliable, and understand others well.
-Their weaknesses are minor since most traits are normal, but being slightly too conventional might sometimes limit flexibility or creativity.</t>
-  </si>
-  <si>
-    <t>Members of this cluster can be described as:  slightly low on reserved,  relatively low on worrisome imaginative,  relatively high on outgoing and carefree</t>
-  </si>
-  <si>
-    <t>Members of this cluster can be described as: normal on outgoing, normal on pensive, relatively high on outgoing, candid, and conventional, slightly high on empathic, normal on casual</t>
-  </si>
-  <si>
-    <t>Members of this cluster can be described as: slightly low on Reserved, very high on grounded, normal on modest, conscientious, and considerate, relatively high on empathic, normal on casual</t>
+    <t>Members of this cluster can be described as:  normal on confident planner,  relatively high on engaged participant,  quite high on creative</t>
+  </si>
+  <si>
+    <t>This cluster comprises highly creative individuals who are very engaged participants, while maintaining a normal level of confidence in their planning.
+Their significant creativity allows them to generate original ideas with ease, and their high engagement means they actively participate and confidently steer their own lives and emotions.
+Despite their strengths, their profound creativity can sometimes lead to feeling overwhelmed by their unique insights, and their self-directed approach may result in less spontaneous emotional connection with others.</t>
+  </si>
+  <si>
+    <t>Members of this cluster can be described as:  normal on principled,  normal on modern anxious,  very high on independent critical</t>
+  </si>
+  <si>
+    <t>This cluster is largely characterized by a profound skepticism towards established institutions, maintaining an average stance on both moral principles and modern anxieties.
+Their strength lies in their highly independent and critical viewpoint, which fosters a diligent scrutiny of government, parliament, and political parties, potentially leading to greater accountability and an emphasis on personal agency.
+A potential weakness of this cluster is the very high level of distrust in vital civic structures, which could impede collective action or faith in the overall system.</t>
+  </si>
+  <si>
+    <t>Members of this cluster can be described as:  slightly low on goal finisher,  normal on offensive conversion,  relatively low on goal-minded</t>
+  </si>
+  <si>
+    <t>Members of this cluster are average at directly scoring and creating chances, but show a reduced emphasis on setting up decisive scoring opportunities for teammates.
+Their strength lies in an average ability to convert attacking opportunities into goals and create high-quality chances for their team.
+However, they are less adept at providing crucial decisive passes and racking up assists, indicating a lower focus on creating scoring opportunities for others.</t>
   </si>
 </sst>
 </file>
@@ -444,28 +444,28 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="140" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="210" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="182" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" ht="210" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="174" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">

--- a/data/describe/few_shot/few_shot_cluster_description.xlsx
+++ b/data/describe/few_shot/few_shot_cluster_description.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\describe\few_shot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA453674-EBD1-4C0D-97DC-64FE61C99234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{248348E7-AE48-497A-A7D2-038DC8F89A56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29940" yWindow="1140" windowWidth="38700" windowHeight="15225" xr2:uid="{75A2F0CC-120C-46DD-B882-D3F79246B1DD}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{75A2F0CC-120C-46DD-B882-D3F79246B1DD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -45,28 +45,28 @@
     <t>Assistant</t>
   </si>
   <si>
-    <t>Members of this cluster can be described as:  normal on confident planner,  relatively high on engaged participant,  quite high on creative</t>
-  </si>
-  <si>
     <t>This cluster comprises highly creative individuals who are very engaged participants, while maintaining a normal level of confidence in their planning.
 Their significant creativity allows them to generate original ideas with ease, and their high engagement means they actively participate and confidently steer their own lives and emotions.
 Despite their strengths, their profound creativity can sometimes lead to feeling overwhelmed by their unique insights, and their self-directed approach may result in less spontaneous emotional connection with others.</t>
   </si>
   <si>
-    <t>Members of this cluster can be described as:  normal on principled,  normal on modern anxious,  very high on independent critical</t>
-  </si>
-  <si>
     <t>This cluster is largely characterized by a profound skepticism towards established institutions, maintaining an average stance on both moral principles and modern anxieties.
 Their strength lies in their highly independent and critical viewpoint, which fosters a diligent scrutiny of government, parliament, and political parties, potentially leading to greater accountability and an emphasis on personal agency.
 A potential weakness of this cluster is the very high level of distrust in vital civic structures, which could impede collective action or faith in the overall system.</t>
   </si>
   <si>
-    <t>Members of this cluster can be described as:  slightly low on goal finisher,  normal on offensive conversion,  relatively low on goal-minded</t>
-  </si>
-  <si>
-    <t>Members of this cluster are average at directly scoring and creating chances, but show a reduced emphasis on setting up decisive scoring opportunities for teammates.
-Their strength lies in an average ability to convert attacking opportunities into goals and create high-quality chances for their team.
-However, they are less adept at providing crucial decisive passes and racking up assists, indicating a lower focus on creating scoring opportunities for others.</t>
+    <t>This cluster describes dogs that are generally calm and stable, with low levels of activity and playfulness, and are slightly less self-reliant, while being average in their social tendencies.
+Their primary strength lies in their calm and stable demeanor, meaning they don't demand extensive mental stimulation or high-energy activities.
+However, they are less inclined towards active play and might be less adaptable to new situations, and they may also exhibit less composure or independence when interacting with other dogs.</t>
+  </si>
+  <si>
+    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical person in that cluster: ```Members of this cluster can be described as:  normal on confident planner,  relatively high on engaged participant,  quite high on creative```</t>
+  </si>
+  <si>
+    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical person in that cluster: ```Members of this cluster can be described as:  normal on principled,  normal on modern anxious,  very high on independent critical```</t>
+  </si>
+  <si>
+    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical dog in that cluster: ```Members of this cluster can be described as:  relatively high on calm and stable,  quite low on active and playful,  slightly low on self-reliant and composed,  normal on social and natural```</t>
   </si>
 </sst>
 </file>
@@ -433,7 +433,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="54.26953125" customWidth="1"/>
-    <col min="2" max="2" width="43" customWidth="1"/>
+    <col min="2" max="2" width="80.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -444,28 +444,28 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="210" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="134" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:2" ht="137.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="210" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
+    <row r="4" spans="1:2" ht="145" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="188.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">

--- a/data/describe/few_shot/few_shot_cluster_description.xlsx
+++ b/data/describe/few_shot/few_shot_cluster_description.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\describe\few_shot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{248348E7-AE48-497A-A7D2-038DC8F89A56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2026FD1-B8F7-46A5-A467-72645216DC36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{75A2F0CC-120C-46DD-B882-D3F79246B1DD}"/>
   </bookViews>
@@ -60,13 +60,13 @@
 However, they are less inclined towards active play and might be less adaptable to new situations, and they may also exhibit less composure or independence when interacting with other dogs.</t>
   </si>
   <si>
-    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical person in that cluster: ```Members of this cluster can be described as:  normal on confident planner,  relatively high on engaged participant,  quite high on creative```</t>
-  </si>
-  <si>
-    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical person in that cluster: ```Members of this cluster can be described as:  normal on principled,  normal on modern anxious,  very high on independent critical```</t>
-  </si>
-  <si>
-    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical dog in that cluster: ```Members of this cluster can be described as:  relatively high on calm and stable,  quite low on active and playful,  slightly low on self-reliant and composed,  normal on social and natural```</t>
+    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical person in that cluster: ```Members of this cluster can be described as:  normal on confident planner,  relatively high on engaged participant,  quite high on creative´´´</t>
+  </si>
+  <si>
+    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical person in that cluster: ```Members of this cluster can be described as:  normal on principled,  normal on modern anxious,  very high on independent critical´´´</t>
+  </si>
+  <si>
+    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical dog in that cluster: ```Members of this cluster can be described as:  relatively high on calm and stable,  quite low on active and playful,  slightly low on self-reliant and composed,  normal on social and natural´´´</t>
   </si>
 </sst>
 </file>
